--- a/reports/dq_scorecard.xlsx
+++ b/reports/dq_scorecard.xlsx
@@ -10,17 +10,18 @@
     <sheet name="Scorecard" sheetId="1" r:id="rId1"/>
     <sheet name="Findings" sheetId="2" r:id="rId2"/>
     <sheet name="Validator vs Truth" sheetId="3" r:id="rId3"/>
-    <sheet name="Rule Catalog" sheetId="4" r:id="rId4"/>
+    <sheet name="Cleaning Log" sheetId="4" r:id="rId4"/>
+    <sheet name="Rule Catalog" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Findings!$A$1:$F$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Findings!$A$1:$F$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="314">
   <si>
     <t>rule_id</t>
   </si>
@@ -88,6 +89,9 @@
     <t>R11</t>
   </si>
   <si>
+    <t>R12</t>
+  </si>
+  <si>
     <t>Duplicate claim_id</t>
   </si>
   <si>
@@ -121,6 +125,9 @@
     <t>Duplicate payment</t>
   </si>
   <si>
+    <t>Possible duplicate billing</t>
+  </si>
+  <si>
     <t>Critical</t>
   </si>
   <si>
@@ -157,7 +164,7 @@
     <t>Rules in breach</t>
   </si>
   <si>
-    <t>6 of 11</t>
+    <t>7 of 12</t>
   </si>
   <si>
     <t>Total findings</t>
@@ -208,376 +215,436 @@
     <t>detail</t>
   </si>
   <si>
+    <t>CLM-102840</t>
+  </si>
+  <si>
+    <t>CLM-104157</t>
+  </si>
+  <si>
+    <t>CLM-104321</t>
+  </si>
+  <si>
+    <t>CLM-100820</t>
+  </si>
+  <si>
+    <t>CLM-100500</t>
+  </si>
+  <si>
+    <t>CLM-100718</t>
+  </si>
+  <si>
+    <t>CLM-103028</t>
+  </si>
+  <si>
+    <t>CLM-104620</t>
+  </si>
+  <si>
+    <t>CLM-104562</t>
+  </si>
+  <si>
     <t>CLM-102304</t>
   </si>
   <si>
-    <t>CLM-100820</t>
-  </si>
-  <si>
-    <t>CLM-104157</t>
-  </si>
-  <si>
-    <t>CLM-104562</t>
-  </si>
-  <si>
-    <t>CLM-104321</t>
-  </si>
-  <si>
-    <t>CLM-100718</t>
-  </si>
-  <si>
-    <t>CLM-103028</t>
-  </si>
-  <si>
-    <t>CLM-100500</t>
-  </si>
-  <si>
     <t>CLM-104945</t>
   </si>
   <si>
-    <t>CLM-102840</t>
-  </si>
-  <si>
     <t>CLM-104288</t>
   </si>
   <si>
-    <t>CLM-104620</t>
+    <t>CLM-101802</t>
+  </si>
+  <si>
+    <t>CLM-100029</t>
+  </si>
+  <si>
+    <t>CLM-101011</t>
+  </si>
+  <si>
+    <t>CLM-103876</t>
+  </si>
+  <si>
+    <t>CLM-104143</t>
+  </si>
+  <si>
+    <t>CLM-102797</t>
+  </si>
+  <si>
+    <t>CLM-101368</t>
   </si>
   <si>
     <t>CLM-102422</t>
   </si>
   <si>
-    <t>CLM-102797</t>
-  </si>
-  <si>
-    <t>CLM-101011</t>
-  </si>
-  <si>
-    <t>CLM-100029</t>
-  </si>
-  <si>
-    <t>CLM-104143</t>
-  </si>
-  <si>
-    <t>CLM-101802</t>
+    <t>CLM-100427</t>
+  </si>
+  <si>
+    <t>CLM-101601</t>
+  </si>
+  <si>
+    <t>CLM-102973</t>
+  </si>
+  <si>
+    <t>CLM-103573</t>
+  </si>
+  <si>
+    <t>CLM-100332</t>
+  </si>
+  <si>
+    <t>CLM-101246</t>
+  </si>
+  <si>
+    <t>CLM-104942</t>
   </si>
   <si>
     <t>CLM-101225</t>
   </si>
   <si>
-    <t>CLM-101246</t>
-  </si>
-  <si>
     <t>CLM-100938</t>
   </si>
   <si>
-    <t>CLM-101368</t>
-  </si>
-  <si>
-    <t>CLM-102973</t>
-  </si>
-  <si>
-    <t>CLM-104942</t>
+    <t>CLM-101636</t>
+  </si>
+  <si>
+    <t>CLM-101850</t>
+  </si>
+  <si>
+    <t>CLM-104624</t>
+  </si>
+  <si>
+    <t>CLM-104530</t>
+  </si>
+  <si>
+    <t>CLM-103112</t>
+  </si>
+  <si>
+    <t>CLM-100956</t>
+  </si>
+  <si>
+    <t>CLM-100974</t>
+  </si>
+  <si>
+    <t>CLM-101021</t>
+  </si>
+  <si>
+    <t>CLM-101312</t>
+  </si>
+  <si>
+    <t>CLM-103432</t>
+  </si>
+  <si>
+    <t>CLM-104125</t>
+  </si>
+  <si>
+    <t>CLM-103823</t>
+  </si>
+  <si>
+    <t>CLM-103419</t>
+  </si>
+  <si>
+    <t>CLM-100413</t>
+  </si>
+  <si>
+    <t>CLM-102988</t>
+  </si>
+  <si>
+    <t>CLM-104057</t>
+  </si>
+  <si>
+    <t>CLM-104066</t>
   </si>
   <si>
     <t>CLM-101742</t>
   </si>
   <si>
-    <t>CLM-100956</t>
-  </si>
-  <si>
-    <t>CLM-101021</t>
-  </si>
-  <si>
-    <t>CLM-100974</t>
-  </si>
-  <si>
-    <t>CLM-104125</t>
-  </si>
-  <si>
-    <t>CLM-103419</t>
-  </si>
-  <si>
-    <t>CLM-101636</t>
-  </si>
-  <si>
-    <t>CLM-101312</t>
-  </si>
-  <si>
-    <t>CLM-104530</t>
-  </si>
-  <si>
-    <t>CLM-103112</t>
-  </si>
-  <si>
     <t>CLM-104932</t>
   </si>
   <si>
-    <t>CLM-103432</t>
-  </si>
-  <si>
-    <t>CLM-103823</t>
-  </si>
-  <si>
-    <t>CLM-104624</t>
-  </si>
-  <si>
     <t>CLM-102385</t>
   </si>
   <si>
     <t>CLM-101018</t>
   </si>
   <si>
+    <t>CLM-103016</t>
+  </si>
+  <si>
+    <t>CLM-100680</t>
+  </si>
+  <si>
+    <t>CLM-103711</t>
+  </si>
+  <si>
+    <t>CLM-100963</t>
+  </si>
+  <si>
+    <t>CLM-103533</t>
+  </si>
+  <si>
+    <t>CLM-100539</t>
+  </si>
+  <si>
+    <t>CLM-101610</t>
+  </si>
+  <si>
+    <t>CLM-101477</t>
+  </si>
+  <si>
+    <t>CLM-103171</t>
+  </si>
+  <si>
     <t>CLM-103302</t>
   </si>
   <si>
-    <t>CLM-100539</t>
-  </si>
-  <si>
     <t>CLM-103990</t>
   </si>
   <si>
-    <t>CLM-101610</t>
-  </si>
-  <si>
-    <t>CLM-100680</t>
-  </si>
-  <si>
-    <t>CLM-101477</t>
-  </si>
-  <si>
-    <t>CLM-100963</t>
-  </si>
-  <si>
-    <t>CLM-103711</t>
-  </si>
-  <si>
-    <t>CLM-103533</t>
-  </si>
-  <si>
-    <t>CLM-103171</t>
-  </si>
-  <si>
     <t>CLM-102359</t>
   </si>
   <si>
-    <t>CLM-103016</t>
+    <t>CLM-102032</t>
+  </si>
+  <si>
+    <t>CLM-103475</t>
   </si>
   <si>
     <t>CLM-103911</t>
   </si>
   <si>
+    <t>CLM-100605</t>
+  </si>
+  <si>
+    <t>CLM-101206</t>
+  </si>
+  <si>
+    <t>CLM-100697</t>
+  </si>
+  <si>
+    <t>CLM-103598</t>
+  </si>
+  <si>
+    <t>CLM-101178</t>
+  </si>
+  <si>
+    <t>CLM-104968</t>
+  </si>
+  <si>
+    <t>CLM-102517</t>
+  </si>
+  <si>
     <t>CLM-104031</t>
   </si>
   <si>
-    <t>CLM-102032</t>
+    <t>CLM-101019</t>
   </si>
   <si>
     <t>CLM-101211</t>
   </si>
   <si>
-    <t>CLM-101178</t>
-  </si>
-  <si>
     <t>CLM-101568</t>
   </si>
   <si>
-    <t>CLM-100697</t>
-  </si>
-  <si>
-    <t>CLM-104968</t>
-  </si>
-  <si>
-    <t>CLM-101206</t>
-  </si>
-  <si>
-    <t>CLM-101019</t>
-  </si>
-  <si>
-    <t>CLM-102517</t>
-  </si>
-  <si>
-    <t>CLM-100605</t>
-  </si>
-  <si>
-    <t>CLM-103598</t>
-  </si>
-  <si>
-    <t>CLM-103475</t>
+    <t>PAY-ORPH-002</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-009</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-005</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-013</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-006</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-014</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-007</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-010</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-003</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-011</t>
   </si>
   <si>
     <t>PAY-ORPH-008</t>
   </si>
   <si>
+    <t>PAY-ORPH-001</t>
+  </si>
+  <si>
+    <t>PAY-ORPH-004</t>
+  </si>
+  <si>
     <t>PAY-ORPH-012</t>
   </si>
   <si>
-    <t>PAY-ORPH-009</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-011</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-006</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-014</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-003</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-001</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-007</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-004</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-010</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-013</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-002</t>
-  </si>
-  <si>
-    <t>PAY-ORPH-005</t>
+    <t>PAY-201427</t>
+  </si>
+  <si>
+    <t>PAY-202259</t>
+  </si>
+  <si>
+    <t>PAY-200562</t>
+  </si>
+  <si>
+    <t>PAY-201321</t>
+  </si>
+  <si>
+    <t>PAY-200286</t>
+  </si>
+  <si>
+    <t>PAY-201889</t>
+  </si>
+  <si>
+    <t>PAY-200101</t>
+  </si>
+  <si>
+    <t>PAY-200689</t>
+  </si>
+  <si>
+    <t>PAY-201803</t>
+  </si>
+  <si>
+    <t>PAY-201070</t>
+  </si>
+  <si>
+    <t>PAY-202119</t>
+  </si>
+  <si>
+    <t>PAY-200606</t>
+  </si>
+  <si>
+    <t>PAY-203229</t>
   </si>
   <si>
     <t>PAY-203647</t>
   </si>
   <si>
-    <t>PAY-203229</t>
-  </si>
-  <si>
-    <t>PAY-202119</t>
-  </si>
-  <si>
-    <t>PAY-201803</t>
-  </si>
-  <si>
-    <t>PAY-200606</t>
-  </si>
-  <si>
-    <t>PAY-200286</t>
-  </si>
-  <si>
-    <t>PAY-202259</t>
-  </si>
-  <si>
-    <t>PAY-201889</t>
-  </si>
-  <si>
-    <t>PAY-201321</t>
-  </si>
-  <si>
-    <t>PAY-201070</t>
-  </si>
-  <si>
-    <t>PAY-200562</t>
-  </si>
-  <si>
-    <t>PAY-200101</t>
-  </si>
-  <si>
-    <t>PAY-200689</t>
-  </si>
-  <si>
-    <t>PAY-201427</t>
+    <t>PAY-201302</t>
+  </si>
+  <si>
+    <t>PAY-200443</t>
+  </si>
+  <si>
+    <t>PAY-203888</t>
+  </si>
+  <si>
+    <t>PAY-203907</t>
+  </si>
+  <si>
+    <t>PAY-203110</t>
+  </si>
+  <si>
+    <t>PAY-201142</t>
+  </si>
+  <si>
+    <t>PAY-203870</t>
+  </si>
+  <si>
+    <t>PAY-203632</t>
   </si>
   <si>
     <t>PAY-203375</t>
   </si>
   <si>
+    <t>PAY-202669</t>
+  </si>
+  <si>
+    <t>PAY-202679</t>
+  </si>
+  <si>
+    <t>PAY-202199</t>
+  </si>
+  <si>
+    <t>PAY-201299</t>
+  </si>
+  <si>
     <t>PAY-203130</t>
   </si>
   <si>
-    <t>PAY-203632</t>
-  </si>
-  <si>
-    <t>PAY-202199</t>
-  </si>
-  <si>
-    <t>PAY-201302</t>
-  </si>
-  <si>
-    <t>PAY-202679</t>
-  </si>
-  <si>
-    <t>PAY-200443</t>
-  </si>
-  <si>
-    <t>PAY-201142</t>
-  </si>
-  <si>
-    <t>PAY-203870</t>
-  </si>
-  <si>
-    <t>PAY-201299</t>
-  </si>
-  <si>
-    <t>PAY-203110</t>
-  </si>
-  <si>
-    <t>PAY-203907</t>
-  </si>
-  <si>
-    <t>PAY-203888</t>
-  </si>
-  <si>
-    <t>PAY-202669</t>
-  </si>
-  <si>
     <t>CLM-104979</t>
   </si>
   <si>
+    <t>CLM-102477</t>
+  </si>
+  <si>
+    <t>CLM-103664</t>
+  </si>
+  <si>
+    <t>CLM-100809</t>
+  </si>
+  <si>
+    <t>CLM-100561</t>
+  </si>
+  <si>
+    <t>CLM-102004</t>
+  </si>
+  <si>
+    <t>CLM-100675</t>
+  </si>
+  <si>
+    <t>CLM-103278</t>
+  </si>
+  <si>
+    <t>CLM-101179</t>
+  </si>
+  <si>
+    <t>CLM-100839</t>
+  </si>
+  <si>
+    <t>CLM-100968</t>
+  </si>
+  <si>
+    <t>CLM-100468</t>
+  </si>
+  <si>
     <t>CLM-101168</t>
   </si>
   <si>
     <t>CLM-102884</t>
   </si>
   <si>
-    <t>CLM-101179</t>
-  </si>
-  <si>
-    <t>CLM-100839</t>
-  </si>
-  <si>
-    <t>CLM-102477</t>
-  </si>
-  <si>
-    <t>CLM-100809</t>
-  </si>
-  <si>
-    <t>CLM-100675</t>
-  </si>
-  <si>
-    <t>CLM-100968</t>
-  </si>
-  <si>
-    <t>CLM-103664</t>
-  </si>
-  <si>
-    <t>CLM-103278</t>
-  </si>
-  <si>
-    <t>CLM-102004</t>
-  </si>
-  <si>
-    <t>CLM-100561</t>
-  </si>
-  <si>
-    <t>CLM-100468</t>
+    <t>CLM-100469</t>
+  </si>
+  <si>
+    <t>CLM-101804</t>
+  </si>
+  <si>
+    <t>CLM-101339</t>
+  </si>
+  <si>
+    <t>CLM-103170</t>
+  </si>
+  <si>
+    <t>CLM-103205</t>
+  </si>
+  <si>
+    <t>CLM-100767</t>
+  </si>
+  <si>
+    <t>CLM-100306</t>
+  </si>
+  <si>
+    <t>CLM-101343</t>
+  </si>
+  <si>
+    <t>CLM-104349</t>
   </si>
   <si>
     <t>CLM-103617</t>
   </si>
   <si>
-    <t>CLM-100306</t>
+    <t>CLM-100252</t>
+  </si>
+  <si>
+    <t>CLM-102012</t>
   </si>
   <si>
     <t>CLM-103053</t>
@@ -586,36 +653,6 @@
     <t>CLM-100210</t>
   </si>
   <si>
-    <t>CLM-104349</t>
-  </si>
-  <si>
-    <t>CLM-100469</t>
-  </si>
-  <si>
-    <t>CLM-103205</t>
-  </si>
-  <si>
-    <t>CLM-100767</t>
-  </si>
-  <si>
-    <t>CLM-101339</t>
-  </si>
-  <si>
-    <t>CLM-101804</t>
-  </si>
-  <si>
-    <t>CLM-103170</t>
-  </si>
-  <si>
-    <t>CLM-101343</t>
-  </si>
-  <si>
-    <t>CLM-102012</t>
-  </si>
-  <si>
-    <t>CLM-100252</t>
-  </si>
-  <si>
     <t>PAY-203962</t>
   </si>
   <si>
@@ -658,6 +695,42 @@
     <t>PAY-203975</t>
   </si>
   <si>
+    <t>CLM-105001</t>
+  </si>
+  <si>
+    <t>CLM-105002</t>
+  </si>
+  <si>
+    <t>CLM-105003</t>
+  </si>
+  <si>
+    <t>CLM-105004</t>
+  </si>
+  <si>
+    <t>CLM-105005</t>
+  </si>
+  <si>
+    <t>CLM-105006</t>
+  </si>
+  <si>
+    <t>CLM-105007</t>
+  </si>
+  <si>
+    <t>CLM-105008</t>
+  </si>
+  <si>
+    <t>CLM-105009</t>
+  </si>
+  <si>
+    <t>CLM-105010</t>
+  </si>
+  <si>
+    <t>CLM-105011</t>
+  </si>
+  <si>
+    <t>CLM-105012</t>
+  </si>
+  <si>
     <t>claim_id appears more than once</t>
   </si>
   <si>
@@ -670,30 +743,30 @@
     <t>cpt_code not in reference table: ABCDE</t>
   </si>
   <si>
+    <t>cpt_code not in reference table: 1234567</t>
+  </si>
+  <si>
+    <t>cpt_code not in reference table: 00000</t>
+  </si>
+  <si>
     <t>cpt_code not in reference table: 99999</t>
   </si>
   <si>
-    <t>cpt_code not in reference table: 00000</t>
-  </si>
-  <si>
-    <t>cpt_code not in reference table: 1234567</t>
+    <t>icd10_code malformed: E119</t>
   </si>
   <si>
     <t>icd10_code malformed: I1O</t>
   </si>
   <si>
+    <t>icd10_code malformed: E11.99999</t>
+  </si>
+  <si>
+    <t>icd10_code malformed: ICD10-E11</t>
+  </si>
+  <si>
     <t>icd10_code malformed: 99.9</t>
   </si>
   <si>
-    <t>icd10_code malformed: E11.99999</t>
-  </si>
-  <si>
-    <t>icd10_code malformed: E119</t>
-  </si>
-  <si>
-    <t>icd10_code malformed: ICD10-E11</t>
-  </si>
-  <si>
     <t>claim_id has no matching claim</t>
   </si>
   <si>
@@ -712,6 +785,9 @@
     <t>same claim, amount and date already paid</t>
   </si>
   <si>
+    <t>same patient, provider, procedure, date and charge as an earlier claim</t>
+  </si>
+  <si>
     <t>true_positives</t>
   </si>
   <si>
@@ -754,6 +830,60 @@
     <t>F1</t>
   </si>
   <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>issue</t>
+  </si>
+  <si>
+    <t>values_corrected</t>
+  </si>
+  <si>
+    <t>claims.claim_id</t>
+  </si>
+  <si>
+    <t>claims.cpt_code</t>
+  </si>
+  <si>
+    <t>claims.icd10_code</t>
+  </si>
+  <si>
+    <t>claims.status</t>
+  </si>
+  <si>
+    <t>payments.claim_id</t>
+  </si>
+  <si>
+    <t>claims.service_date</t>
+  </si>
+  <si>
+    <t>payments.payment_date</t>
+  </si>
+  <si>
+    <t>claims.charge_amount</t>
+  </si>
+  <si>
+    <t>spacing / letter case</t>
+  </si>
+  <si>
+    <t>US date format converted</t>
+  </si>
+  <si>
+    <t>currency text converted</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Values Corrected</t>
+  </si>
+  <si>
+    <t>Formatting fixes are corrected automatically and are NOT counted as failures.</t>
+  </si>
+  <si>
     <t>Rule ID</t>
   </si>
   <si>
@@ -796,6 +926,9 @@
     <t>same claim_id, paid_amount and payment_date appear more than once</t>
   </si>
   <si>
+    <t>different claim_id but same patient, provider, procedure, date and charge</t>
+  </si>
+  <si>
     <t>Double billing; inflated revenue and duplicate payment risk</t>
   </si>
   <si>
@@ -827,6 +960,9 @@
   </si>
   <si>
     <t>Cash overstated; possible overpayment to recover</t>
+  </si>
+  <si>
+    <t>Likely double billing under a new claim number; compliance risk</t>
   </si>
 </sst>
 </file>
@@ -1015,9 +1151,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Scorecard!$A$7:$A$17</c:f>
+              <c:f>Scorecard!$A$7:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>R01</c:v>
                 </c:pt>
@@ -1051,29 +1187,32 @@
                 <c:pt idx="10">
                   <c:v>R11</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>R12</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Scorecard!$F$7:$F$17</c:f>
+              <c:f>Scorecard!$F$7:$F$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>14</c:v>
@@ -1092,6 +1231,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1143,13 +1285,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1457,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -1471,79 +1613,79 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1">
-        <v>5000</v>
+        <v>5052</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1">
-        <v>3975</v>
+        <v>3990</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H3" s="1">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J3" s="7">
-        <v>76976.52</v>
+        <v>85846.15000000001</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1551,31 +1693,31 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1">
-        <v>5000</v>
+        <v>5052</v>
       </c>
       <c r="F7" s="1">
         <v>12</v>
       </c>
       <c r="G7" s="2">
-        <v>0.0024</v>
+        <v>0.002375296912114014</v>
       </c>
       <c r="H7" s="2">
-        <v>0.9976</v>
+        <v>0.997624703087886</v>
       </c>
       <c r="I7" s="2">
         <v>0.001</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K7" s="3">
         <v>5391.82</v>
@@ -1586,34 +1728,34 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1">
-        <v>5000</v>
+        <v>5052</v>
       </c>
       <c r="F8" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G8" s="2">
-        <v>0.0024</v>
+        <v>0.003365003958828187</v>
       </c>
       <c r="H8" s="2">
-        <v>0.9976</v>
+        <v>0.9966349960411718</v>
       </c>
       <c r="I8" s="2">
         <v>0.005</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K8" s="3">
-        <v>3532.2</v>
+        <v>6036.16</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1621,34 +1763,34 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1">
-        <v>5000</v>
+        <v>5052</v>
       </c>
       <c r="F9" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G9" s="2">
-        <v>0.0028</v>
+        <v>0.003760886777513856</v>
       </c>
       <c r="H9" s="2">
-        <v>0.9972</v>
+        <v>0.9962391132224862</v>
       </c>
       <c r="I9" s="2">
         <v>0.005</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K9" s="3">
-        <v>9698.92</v>
+        <v>11881.78</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1656,34 +1798,34 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1">
-        <v>5000</v>
+        <v>5052</v>
       </c>
       <c r="F10" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G10" s="2">
-        <v>0.0028</v>
+        <v>0.003760886777513856</v>
       </c>
       <c r="H10" s="2">
-        <v>0.9972</v>
+        <v>0.9962391132224862</v>
       </c>
       <c r="I10" s="2">
         <v>0.005</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K10" s="3">
-        <v>5747.54</v>
+        <v>3243.58</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1691,34 +1833,34 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1">
-        <v>5000</v>
+        <v>5052</v>
       </c>
       <c r="F11" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G11" s="2">
-        <v>0.0028</v>
+        <v>0.003760886777513856</v>
       </c>
       <c r="H11" s="2">
-        <v>0.9972</v>
+        <v>0.9962391132224862</v>
       </c>
       <c r="I11" s="2">
         <v>0.005</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K11" s="3">
-        <v>9454.02</v>
+        <v>11636.88</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1726,31 +1868,31 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1">
-        <v>3975</v>
+        <v>3990</v>
       </c>
       <c r="F12" s="1">
         <v>14</v>
       </c>
       <c r="G12" s="2">
-        <v>0.003522012578616352</v>
+        <v>0.003508771929824561</v>
       </c>
       <c r="H12" s="2">
-        <v>0.9964779874213836</v>
+        <v>0.9964912280701754</v>
       </c>
       <c r="I12" s="2">
         <v>0.001</v>
       </c>
       <c r="J12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K12" s="3">
         <v>12337.8</v>
@@ -1761,31 +1903,31 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E13" s="1">
-        <v>3961</v>
+        <v>3976</v>
       </c>
       <c r="F13" s="1">
         <v>14</v>
       </c>
       <c r="G13" s="2">
-        <v>0.003534460994698309</v>
+        <v>0.00352112676056338</v>
       </c>
       <c r="H13" s="2">
-        <v>0.9964655390053017</v>
+        <v>0.9964788732394366</v>
       </c>
       <c r="I13" s="2">
         <v>0.001</v>
       </c>
       <c r="J13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K13" s="3">
         <v>1203.74</v>
@@ -1796,31 +1938,31 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14" s="1">
-        <v>3961</v>
+        <v>3976</v>
       </c>
       <c r="F14" s="1">
         <v>14</v>
       </c>
       <c r="G14" s="2">
-        <v>0.003534460994698309</v>
+        <v>0.00352112676056338</v>
       </c>
       <c r="H14" s="2">
-        <v>0.9964655390053017</v>
+        <v>0.9964788732394366</v>
       </c>
       <c r="I14" s="2">
         <v>0.005</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K14" s="3">
         <v>5535.9</v>
@@ -1831,13 +1973,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1">
         <v>3352</v>
@@ -1855,7 +1997,7 @@
         <v>0.001</v>
       </c>
       <c r="J15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K15" s="3">
         <v>11488.2</v>
@@ -1866,13 +2008,13 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E16" s="1">
         <v>609</v>
@@ -1890,7 +2032,7 @@
         <v>0.01</v>
       </c>
       <c r="J16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K16" s="3">
         <v>5475.14</v>
@@ -1901,38 +2043,73 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="1">
-        <v>3975</v>
+        <v>3990</v>
       </c>
       <c r="F17" s="1">
         <v>14</v>
       </c>
       <c r="G17" s="2">
-        <v>0.003522012578616352</v>
+        <v>0.003508771929824561</v>
       </c>
       <c r="H17" s="2">
-        <v>0.9964779874213836</v>
+        <v>0.9964912280701754</v>
       </c>
       <c r="I17" s="2">
         <v>0.001</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K17" s="3">
         <v>7111.24</v>
       </c>
     </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5052</v>
+      </c>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.002375296912114014</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.997624703087886</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.001</v>
+      </c>
+      <c r="J18" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" s="3">
+        <v>4503.91</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J7:J17">
+  <conditionalFormatting sqref="J7:J18">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="breach">
       <formula>NOT(ISERROR(SEARCH("breach",J7)))</formula>
     </cfRule>
@@ -1947,7 +2124,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -1963,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>10</v>
@@ -1983,19 +2160,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F2" s="3">
-        <v>1183.24</v>
+        <v>294.23</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2003,19 +2180,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F3" s="3">
-        <v>116.67</v>
+        <v>177.84</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2023,19 +2200,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F4" s="3">
-        <v>177.84</v>
+        <v>796.12</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2043,19 +2220,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F5" s="3">
-        <v>776</v>
+        <v>116.67</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2063,19 +2240,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F6" s="3">
-        <v>796.12</v>
+        <v>249.59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2083,16 +2260,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F7" s="3">
         <v>554.4</v>
@@ -2103,16 +2280,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F8" s="3">
         <v>66.55</v>
@@ -2123,19 +2300,19 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F9" s="3">
-        <v>249.59</v>
+        <v>306.54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2143,19 +2320,19 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F10" s="3">
-        <v>733.75</v>
+        <v>776</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2163,19 +2340,19 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F11" s="3">
-        <v>294.23</v>
+        <v>1183.24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2183,19 +2360,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F12" s="3">
-        <v>136.89</v>
+        <v>733.75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2203,19 +2380,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F13" s="3">
-        <v>306.54</v>
+        <v>136.89</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2223,19 +2400,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F14" s="3">
-        <v>60.33</v>
+        <v>291.19</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2243,19 +2420,19 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F15" s="3">
-        <v>221.99</v>
+        <v>198.39</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2263,16 +2440,16 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F16" s="3">
         <v>916.38</v>
@@ -2283,19 +2460,19 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F17" s="3">
-        <v>198.39</v>
+        <v>111.82</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2303,16 +2480,16 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F18" s="3">
         <v>253.28</v>
@@ -2323,19 +2500,19 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F19" s="3">
-        <v>291.19</v>
+        <v>221.99</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2343,19 +2520,19 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F20" s="3">
-        <v>145.6</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2363,19 +2540,19 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F21" s="3">
-        <v>241.9</v>
+        <v>60.33</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2383,19 +2560,19 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F22" s="3">
-        <v>733.5599999999999</v>
+        <v>268.23</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2403,19 +2580,19 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F23" s="3">
-        <v>53.48</v>
+        <v>1743.34</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2423,16 +2600,16 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F24" s="3">
         <v>335.26</v>
@@ -2443,119 +2620,119 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F25" s="3">
-        <v>80.84</v>
+        <v>325.12</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="F26" s="3">
-        <v>430.27</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="F27" s="3">
-        <v>1479.7</v>
+        <v>241.9</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="F28" s="3">
-        <v>250.52</v>
+        <v>80.84</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="F29" s="3">
-        <v>570.0599999999999</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="F30" s="3">
-        <v>588.62</v>
+        <v>733.5599999999999</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2563,19 +2740,19 @@
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F31" s="3">
-        <v>2438.14</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2583,19 +2760,19 @@
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E32" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F32" s="3">
-        <v>49.95</v>
+        <v>1065.55</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2603,19 +2780,19 @@
         <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F33" s="3">
-        <v>326.08</v>
+        <v>530.6900000000001</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2623,16 +2800,16 @@
         <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F34" s="3">
         <v>728.78</v>
@@ -2643,16 +2820,16 @@
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F35" s="3">
         <v>867.33</v>
@@ -2663,19 +2840,19 @@
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F36" s="3">
-        <v>688.11</v>
+        <v>1479.7</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2683,19 +2860,19 @@
         <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E37" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F37" s="3">
-        <v>596.1</v>
+        <v>570.0599999999999</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2703,19 +2880,19 @@
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F38" s="3">
-        <v>154.57</v>
+        <v>250.52</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2723,219 +2900,219 @@
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F39" s="3">
-        <v>530.6900000000001</v>
+        <v>326.08</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
         <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E40" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="F40" s="3">
-        <v>92.23</v>
+        <v>596.1</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
         <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E41" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="F41" s="3">
-        <v>296.44</v>
+        <v>588.62</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
         <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E42" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="F42" s="3">
-        <v>1887.79</v>
+        <v>154.57</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
         <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D43" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E43" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="F43" s="3">
-        <v>185.08</v>
+        <v>2438.14</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B44" t="s">
         <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="F44" s="3">
-        <v>153.93</v>
+        <v>426.74</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
         <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="F45" s="3">
-        <v>282.69</v>
+        <v>487.58</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
         <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D46" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E46" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="F46" s="3">
-        <v>276.89</v>
+        <v>174.44</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
         <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E47" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="F47" s="3">
-        <v>74.11</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
         <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E48" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="F48" s="3">
-        <v>252.54</v>
+        <v>430.27</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
         <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E49" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="F49" s="3">
-        <v>931.5599999999999</v>
+        <v>688.11</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2943,19 +3120,19 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E50" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="F50" s="3">
-        <v>859.9299999999999</v>
+        <v>92.23</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2963,19 +3140,19 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D51" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="F51" s="3">
-        <v>186.28</v>
+        <v>296.44</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2983,19 +3160,19 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D52" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="E52" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="F52" s="3">
-        <v>220.14</v>
+        <v>-111.82</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3003,16 +3180,16 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E53" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="F53" s="3">
         <v>47.93</v>
@@ -3020,1973 +3197,2613 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54" t="s">
         <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E54" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="F54" s="3">
-        <v>138.58</v>
+        <v>276.89</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E55" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="F55" s="3">
-        <v>64.84999999999999</v>
+        <v>931.5599999999999</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s">
         <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E56" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="F56" s="3">
-        <v>245.55</v>
+        <v>252.54</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s">
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E57" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="F57" s="3">
-        <v>72.48999999999999</v>
+        <v>859.9299999999999</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s">
         <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="F58" s="3">
-        <v>61.65</v>
+        <v>185.08</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s">
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D59" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="E59" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="F59" s="3">
-        <v>229.21</v>
+        <v>-268.23</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B60" t="s">
         <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D60" t="s">
         <v>120</v>
       </c>
       <c r="E60" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="F60" s="3">
-        <v>290.55</v>
+        <v>282.69</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s">
         <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D61" t="s">
         <v>121</v>
       </c>
       <c r="E61" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="F61" s="3">
-        <v>1323.79</v>
+        <v>74.11</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B62" t="s">
         <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E62" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F62" s="3">
-        <v>86.5</v>
+        <v>-1743.34</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E63" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="F63" s="3">
-        <v>2101.17</v>
+        <v>186.28</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
         <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="E64" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F64" s="3">
-        <v>119.05</v>
+        <v>-325.12</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
         <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E65" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="F65" s="3">
-        <v>1028.91</v>
+        <v>1887.79</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
         <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="F66" s="3">
-        <v>2107.41</v>
+        <v>153.93</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D67" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="E67" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="F67" s="3">
-        <v>1584.31</v>
+        <v>-55.45</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D68" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E68" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="F68" s="3">
-        <v>829.41</v>
+        <v>220.14</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B69" t="s">
         <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D69" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E69" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="F69" s="3">
-        <v>302.81</v>
+        <v>1065.55</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B70" t="s">
         <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D70" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E70" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="F70" s="3">
-        <v>775.76</v>
+        <v>245.55</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B71" t="s">
         <v>27</v>
       </c>
       <c r="C71" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D71" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E71" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="F71" s="3">
-        <v>1036.71</v>
+        <v>1584.31</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B72" t="s">
         <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D72" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E72" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="F72" s="3">
-        <v>652.67</v>
+        <v>138.58</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B73" t="s">
         <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D73" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E73" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="F73" s="3">
-        <v>1770.53</v>
+        <v>1028.91</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B74" t="s">
         <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D74" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E74" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F74" s="3">
-        <v>1875.63</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B75" t="s">
         <v>27</v>
       </c>
       <c r="C75" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D75" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E75" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="F75" s="3">
-        <v>258.77</v>
+        <v>290.55</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B76" t="s">
         <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D76" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E76" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="F76" s="3">
-        <v>435.32</v>
+        <v>2107.41</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B77" t="s">
         <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E77" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="F77" s="3">
-        <v>378.33</v>
+        <v>61.65</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B78" t="s">
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D78" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E78" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="F78" s="3">
-        <v>261.99</v>
+        <v>1323.79</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B79" t="s">
         <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E79" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F79" s="3">
-        <v>1723.49</v>
+        <v>119.05</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
         <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D80" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E80" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="F80" s="3">
-        <v>1041.94</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
         <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="E81" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F81" s="3">
-        <v>994.4400000000001</v>
+        <v>426.74</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C82" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D82" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="E82" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="F82" s="3">
-        <v>8.44</v>
+        <v>487.58</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C83" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E83" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="F83" s="3">
-        <v>6.5</v>
+        <v>2101.17</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C84" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D84" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="E84" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="F84" s="3">
-        <v>66.58</v>
+        <v>174.44</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C85" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="E85" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="F85" s="3">
-        <v>234.8</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E86" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="F86" s="3">
-        <v>122.81</v>
+        <v>72.48999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D87" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E87" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="F87" s="3">
-        <v>58.45</v>
+        <v>229.21</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B88" t="s">
         <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D88" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E88" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F88" s="3">
-        <v>113.6</v>
+        <v>1041.94</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B89" t="s">
         <v>28</v>
       </c>
       <c r="C89" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D89" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E89" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F89" s="3">
-        <v>109.52</v>
+        <v>775.76</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B90" t="s">
         <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D90" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E90" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F90" s="3">
-        <v>21.37</v>
+        <v>994.4400000000001</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B91" t="s">
         <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D91" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E91" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F91" s="3">
-        <v>339.06</v>
+        <v>1723.49</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B92" t="s">
         <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D92" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E92" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F92" s="3">
-        <v>18.76</v>
+        <v>652.67</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B93" t="s">
         <v>28</v>
       </c>
       <c r="C93" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D93" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E93" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F93" s="3">
-        <v>24.51</v>
+        <v>1770.53</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B94" t="s">
         <v>28</v>
       </c>
       <c r="C94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D94" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E94" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F94" s="3">
-        <v>23.32</v>
+        <v>435.32</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B95" t="s">
         <v>28</v>
       </c>
       <c r="C95" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D95" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E95" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F95" s="3">
-        <v>56.02</v>
+        <v>261.99</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C96" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D96" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E96" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F96" s="3">
-        <v>1663.03</v>
+        <v>1875.63</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C97" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D97" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E97" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F97" s="3">
-        <v>1257.47</v>
+        <v>1036.71</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C98" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D98" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E98" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F98" s="3">
-        <v>123.17</v>
+        <v>829.41</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C99" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D99" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E99" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F99" s="3">
-        <v>215.73</v>
+        <v>258.77</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C100" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D100" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E100" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F100" s="3">
-        <v>274.11</v>
+        <v>378.33</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C101" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D101" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E101" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F101" s="3">
-        <v>768.36</v>
+        <v>302.81</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
         <v>29</v>
       </c>
       <c r="C102" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D102" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E102" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F102" s="3">
-        <v>47.01</v>
+        <v>56.02</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
         <v>29</v>
       </c>
       <c r="C103" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D103" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E103" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F103" s="3">
-        <v>68.77</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
         <v>29</v>
       </c>
       <c r="C104" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D104" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E104" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F104" s="3">
-        <v>159.77</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
         <v>29</v>
       </c>
       <c r="C105" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D105" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E105" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F105" s="3">
-        <v>234.91</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
         <v>29</v>
       </c>
       <c r="C106" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D106" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E106" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F106" s="3">
-        <v>53.16</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
         <v>29</v>
       </c>
       <c r="C107" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D107" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E107" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F107" s="3">
-        <v>112.14</v>
+        <v>109.52</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
         <v>29</v>
       </c>
       <c r="C108" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D108" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E108" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F108" s="3">
-        <v>506.05</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B109" t="s">
         <v>29</v>
       </c>
       <c r="C109" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D109" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E109" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F109" s="3">
-        <v>52.22</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C110" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D110" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E110" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="F110" s="3">
-        <v>1606.15</v>
+        <v>234.8</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C111" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D111" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E111" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="F111" s="3">
-        <v>108.26</v>
+        <v>339.06</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C112" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D112" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E112" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="F112" s="3">
-        <v>78.40000000000001</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C113" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D113" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E113" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="F113" s="3">
-        <v>148.06</v>
+        <v>122.81</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C114" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D114" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E114" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="F114" s="3">
-        <v>44.73</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C115" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D115" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E115" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="F115" s="3">
-        <v>1440.02</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B116" t="s">
         <v>30</v>
       </c>
       <c r="C116" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D116" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E116" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F116" s="3">
-        <v>441.75</v>
+        <v>274.11</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B117" t="s">
         <v>30</v>
       </c>
       <c r="C117" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D117" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E117" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F117" s="3">
-        <v>428.45</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B118" t="s">
         <v>30</v>
       </c>
       <c r="C118" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D118" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E118" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F118" s="3">
-        <v>1568.97</v>
+        <v>506.05</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B119" t="s">
         <v>30</v>
       </c>
       <c r="C119" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D119" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E119" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F119" s="3">
-        <v>406.82</v>
+        <v>112.14</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B120" t="s">
         <v>30</v>
       </c>
       <c r="C120" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D120" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E120" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F120" s="3">
-        <v>1107.31</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B121" t="s">
         <v>30</v>
       </c>
       <c r="C121" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D121" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E121" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F121" s="3">
-        <v>2469.33</v>
+        <v>68.77</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B122" t="s">
         <v>30</v>
       </c>
       <c r="C122" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D122" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E122" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F122" s="3">
-        <v>1191.11</v>
+        <v>159.77</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B123" t="s">
         <v>30</v>
       </c>
       <c r="C123" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D123" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E123" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="F123" s="3">
-        <v>448.84</v>
+        <v>123.17</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C124" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D124" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E124" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="F124" s="3">
-        <v>200.51</v>
+        <v>1663.03</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C125" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D125" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E125" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="F125" s="3">
-        <v>346.07</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C126" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D126" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E126" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="F126" s="3">
-        <v>1592.11</v>
+        <v>768.36</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B127" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C127" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D127" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E127" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="F127" s="3">
-        <v>49.67</v>
+        <v>215.73</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C128" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D128" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E128" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="F128" s="3">
-        <v>131</v>
+        <v>234.91</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C129" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D129" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E129" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="F129" s="3">
-        <v>91.08</v>
+        <v>1257.47</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B130" t="s">
         <v>31</v>
       </c>
       <c r="C130" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D130" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E130" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F130" s="3">
-        <v>1733.67</v>
+        <v>1606.15</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B131" t="s">
         <v>31</v>
       </c>
       <c r="C131" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D131" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E131" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F131" s="3">
-        <v>193.85</v>
+        <v>1440.02</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B132" t="s">
         <v>31</v>
       </c>
       <c r="C132" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D132" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E132" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F132" s="3">
-        <v>108.64</v>
+        <v>406.82</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B133" t="s">
         <v>31</v>
       </c>
       <c r="C133" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D133" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E133" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F133" s="3">
-        <v>524.96</v>
+        <v>441.75</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B134" t="s">
         <v>31</v>
       </c>
       <c r="C134" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D134" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E134" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F134" s="3">
-        <v>77.84</v>
+        <v>1191.11</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B135" t="s">
         <v>31</v>
       </c>
       <c r="C135" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D135" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E135" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F135" s="3">
-        <v>73.54000000000001</v>
+        <v>2469.33</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B136" t="s">
         <v>31</v>
       </c>
       <c r="C136" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D136" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E136" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F136" s="3">
-        <v>190.84</v>
+        <v>428.45</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B137" t="s">
         <v>31</v>
       </c>
       <c r="C137" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D137" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E137" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F137" s="3">
-        <v>161.36</v>
+        <v>1107.31</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C138" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D138" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E138" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F138" s="3">
-        <v>1756.9</v>
+        <v>148.06</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B139" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C139" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D139" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E139" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F139" s="3">
-        <v>88.95</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B140" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C140" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D140" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E140" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F140" s="3">
-        <v>264.79</v>
+        <v>1568.97</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C141" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D141" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E141" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F141" s="3">
-        <v>2027.13</v>
+        <v>448.84</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B142" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C142" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D142" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E142" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F142" s="3">
-        <v>512.76</v>
+        <v>108.26</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B143" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C143" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D143" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E143" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F143" s="3">
-        <v>124.8</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B144" t="s">
         <v>32</v>
       </c>
       <c r="C144" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D144" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E144" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F144" s="3">
-        <v>184.51</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B145" t="s">
         <v>32</v>
       </c>
       <c r="C145" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D145" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E145" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F145" s="3">
-        <v>284.04</v>
+        <v>524.96</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B146" t="s">
         <v>32</v>
       </c>
       <c r="C146" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D146" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E146" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F146" s="3">
-        <v>156.02</v>
+        <v>108.64</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B147" t="s">
         <v>32</v>
       </c>
       <c r="C147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D147" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E147" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F147" s="3">
-        <v>731.9</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B148" t="s">
         <v>32</v>
       </c>
       <c r="C148" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D148" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E148" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F148" s="3">
-        <v>54.9</v>
+        <v>1733.67</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B149" t="s">
         <v>32</v>
       </c>
       <c r="C149" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D149" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E149" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F149" s="3">
-        <v>700.67</v>
+        <v>193.85</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B150" t="s">
         <v>32</v>
       </c>
       <c r="C150" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D150" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E150" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F150" s="3">
-        <v>50.6</v>
+        <v>346.07</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B151" t="s">
         <v>32</v>
       </c>
       <c r="C151" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D151" t="s">
+        <v>203</v>
+      </c>
+      <c r="E151" t="s">
+        <v>252</v>
+      </c>
+      <c r="F151" s="3">
+        <v>73.54000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>20</v>
+      </c>
+      <c r="B152" t="s">
+        <v>32</v>
+      </c>
+      <c r="C152" t="s">
+        <v>38</v>
+      </c>
+      <c r="D152" t="s">
+        <v>204</v>
+      </c>
+      <c r="E152" t="s">
+        <v>252</v>
+      </c>
+      <c r="F152" s="3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>20</v>
+      </c>
+      <c r="B153" t="s">
+        <v>32</v>
+      </c>
+      <c r="C153" t="s">
+        <v>38</v>
+      </c>
+      <c r="D153" t="s">
+        <v>205</v>
+      </c>
+      <c r="E153" t="s">
+        <v>252</v>
+      </c>
+      <c r="F153" s="3">
+        <v>200.51</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>20</v>
+      </c>
+      <c r="B154" t="s">
+        <v>32</v>
+      </c>
+      <c r="C154" t="s">
+        <v>38</v>
+      </c>
+      <c r="D154" t="s">
+        <v>206</v>
+      </c>
+      <c r="E154" t="s">
+        <v>252</v>
+      </c>
+      <c r="F154" s="3">
+        <v>161.36</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>20</v>
+      </c>
+      <c r="B155" t="s">
+        <v>32</v>
+      </c>
+      <c r="C155" t="s">
+        <v>38</v>
+      </c>
+      <c r="D155" t="s">
+        <v>207</v>
+      </c>
+      <c r="E155" t="s">
+        <v>252</v>
+      </c>
+      <c r="F155" s="3">
+        <v>190.84</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>20</v>
+      </c>
+      <c r="B156" t="s">
+        <v>32</v>
+      </c>
+      <c r="C156" t="s">
+        <v>38</v>
+      </c>
+      <c r="D156" t="s">
+        <v>208</v>
+      </c>
+      <c r="E156" t="s">
+        <v>252</v>
+      </c>
+      <c r="F156" s="3">
+        <v>1592.11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>20</v>
+      </c>
+      <c r="B157" t="s">
+        <v>32</v>
+      </c>
+      <c r="C157" t="s">
+        <v>38</v>
+      </c>
+      <c r="D157" t="s">
+        <v>209</v>
+      </c>
+      <c r="E157" t="s">
+        <v>252</v>
+      </c>
+      <c r="F157" s="3">
+        <v>49.67</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>21</v>
+      </c>
+      <c r="B158" t="s">
+        <v>33</v>
+      </c>
+      <c r="C158" t="s">
+        <v>39</v>
+      </c>
+      <c r="D158" t="s">
+        <v>210</v>
+      </c>
+      <c r="E158" t="s">
+        <v>253</v>
+      </c>
+      <c r="F158" s="3">
+        <v>1756.9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>21</v>
+      </c>
+      <c r="B159" t="s">
+        <v>33</v>
+      </c>
+      <c r="C159" t="s">
+        <v>39</v>
+      </c>
+      <c r="D159" t="s">
         <v>211</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E159" t="s">
+        <v>253</v>
+      </c>
+      <c r="F159" s="3">
+        <v>88.95</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>21</v>
+      </c>
+      <c r="B160" t="s">
+        <v>33</v>
+      </c>
+      <c r="C160" t="s">
+        <v>39</v>
+      </c>
+      <c r="D160" t="s">
+        <v>212</v>
+      </c>
+      <c r="E160" t="s">
+        <v>253</v>
+      </c>
+      <c r="F160" s="3">
+        <v>264.79</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>21</v>
+      </c>
+      <c r="B161" t="s">
+        <v>33</v>
+      </c>
+      <c r="C161" t="s">
+        <v>39</v>
+      </c>
+      <c r="D161" t="s">
+        <v>213</v>
+      </c>
+      <c r="E161" t="s">
+        <v>253</v>
+      </c>
+      <c r="F161" s="3">
+        <v>2027.13</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>21</v>
+      </c>
+      <c r="B162" t="s">
+        <v>33</v>
+      </c>
+      <c r="C162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D162" t="s">
+        <v>214</v>
+      </c>
+      <c r="E162" t="s">
+        <v>253</v>
+      </c>
+      <c r="F162" s="3">
+        <v>512.76</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>21</v>
+      </c>
+      <c r="B163" t="s">
+        <v>33</v>
+      </c>
+      <c r="C163" t="s">
+        <v>39</v>
+      </c>
+      <c r="D163" t="s">
+        <v>215</v>
+      </c>
+      <c r="E163" t="s">
+        <v>253</v>
+      </c>
+      <c r="F163" s="3">
+        <v>124.8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>21</v>
+      </c>
+      <c r="B164" t="s">
+        <v>33</v>
+      </c>
+      <c r="C164" t="s">
+        <v>39</v>
+      </c>
+      <c r="D164" t="s">
+        <v>216</v>
+      </c>
+      <c r="E164" t="s">
+        <v>253</v>
+      </c>
+      <c r="F164" s="3">
+        <v>184.51</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>21</v>
+      </c>
+      <c r="B165" t="s">
+        <v>33</v>
+      </c>
+      <c r="C165" t="s">
+        <v>39</v>
+      </c>
+      <c r="D165" t="s">
+        <v>217</v>
+      </c>
+      <c r="E165" t="s">
+        <v>253</v>
+      </c>
+      <c r="F165" s="3">
+        <v>284.04</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>21</v>
+      </c>
+      <c r="B166" t="s">
+        <v>33</v>
+      </c>
+      <c r="C166" t="s">
+        <v>39</v>
+      </c>
+      <c r="D166" t="s">
+        <v>218</v>
+      </c>
+      <c r="E166" t="s">
+        <v>253</v>
+      </c>
+      <c r="F166" s="3">
+        <v>156.02</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>21</v>
+      </c>
+      <c r="B167" t="s">
+        <v>33</v>
+      </c>
+      <c r="C167" t="s">
+        <v>39</v>
+      </c>
+      <c r="D167" t="s">
+        <v>219</v>
+      </c>
+      <c r="E167" t="s">
+        <v>253</v>
+      </c>
+      <c r="F167" s="3">
+        <v>731.9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>21</v>
+      </c>
+      <c r="B168" t="s">
+        <v>33</v>
+      </c>
+      <c r="C168" t="s">
+        <v>39</v>
+      </c>
+      <c r="D168" t="s">
+        <v>220</v>
+      </c>
+      <c r="E168" t="s">
+        <v>253</v>
+      </c>
+      <c r="F168" s="3">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>21</v>
+      </c>
+      <c r="B169" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169" t="s">
+        <v>39</v>
+      </c>
+      <c r="D169" t="s">
+        <v>221</v>
+      </c>
+      <c r="E169" t="s">
+        <v>253</v>
+      </c>
+      <c r="F169" s="3">
+        <v>700.67</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>21</v>
+      </c>
+      <c r="B170" t="s">
+        <v>33</v>
+      </c>
+      <c r="C170" t="s">
+        <v>39</v>
+      </c>
+      <c r="D170" t="s">
+        <v>222</v>
+      </c>
+      <c r="E170" t="s">
+        <v>253</v>
+      </c>
+      <c r="F170" s="3">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>21</v>
+      </c>
+      <c r="B171" t="s">
+        <v>33</v>
+      </c>
+      <c r="C171" t="s">
+        <v>39</v>
+      </c>
+      <c r="D171" t="s">
+        <v>223</v>
+      </c>
+      <c r="E171" t="s">
+        <v>253</v>
+      </c>
+      <c r="F171" s="3">
+        <v>173.27</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>22</v>
+      </c>
+      <c r="B172" t="s">
+        <v>34</v>
+      </c>
+      <c r="C172" t="s">
+        <v>38</v>
+      </c>
+      <c r="D172" t="s">
+        <v>224</v>
+      </c>
+      <c r="E172" t="s">
+        <v>254</v>
+      </c>
+      <c r="F172" s="3">
+        <v>240.9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>22</v>
+      </c>
+      <c r="B173" t="s">
+        <v>34</v>
+      </c>
+      <c r="C173" t="s">
+        <v>38</v>
+      </c>
+      <c r="D173" t="s">
+        <v>225</v>
+      </c>
+      <c r="E173" t="s">
+        <v>254</v>
+      </c>
+      <c r="F173" s="3">
+        <v>215.88</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>22</v>
+      </c>
+      <c r="B174" t="s">
+        <v>34</v>
+      </c>
+      <c r="C174" t="s">
+        <v>38</v>
+      </c>
+      <c r="D174" t="s">
+        <v>226</v>
+      </c>
+      <c r="E174" t="s">
+        <v>254</v>
+      </c>
+      <c r="F174" s="3">
+        <v>463.27</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>22</v>
+      </c>
+      <c r="B175" t="s">
+        <v>34</v>
+      </c>
+      <c r="C175" t="s">
+        <v>38</v>
+      </c>
+      <c r="D175" t="s">
+        <v>227</v>
+      </c>
+      <c r="E175" t="s">
+        <v>254</v>
+      </c>
+      <c r="F175" s="3">
+        <v>133.75</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>22</v>
+      </c>
+      <c r="B176" t="s">
+        <v>34</v>
+      </c>
+      <c r="C176" t="s">
+        <v>38</v>
+      </c>
+      <c r="D176" t="s">
+        <v>228</v>
+      </c>
+      <c r="E176" t="s">
+        <v>254</v>
+      </c>
+      <c r="F176" s="3">
+        <v>805.27</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>22</v>
+      </c>
+      <c r="B177" t="s">
+        <v>34</v>
+      </c>
+      <c r="C177" t="s">
+        <v>38</v>
+      </c>
+      <c r="D177" t="s">
         <v>229</v>
       </c>
-      <c r="F151" s="3">
-        <v>173.27</v>
+      <c r="E177" t="s">
+        <v>254</v>
+      </c>
+      <c r="F177" s="3">
+        <v>231.72</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>22</v>
+      </c>
+      <c r="B178" t="s">
+        <v>34</v>
+      </c>
+      <c r="C178" t="s">
+        <v>38</v>
+      </c>
+      <c r="D178" t="s">
+        <v>230</v>
+      </c>
+      <c r="E178" t="s">
+        <v>254</v>
+      </c>
+      <c r="F178" s="3">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>22</v>
+      </c>
+      <c r="B179" t="s">
+        <v>34</v>
+      </c>
+      <c r="C179" t="s">
+        <v>38</v>
+      </c>
+      <c r="D179" t="s">
+        <v>231</v>
+      </c>
+      <c r="E179" t="s">
+        <v>254</v>
+      </c>
+      <c r="F179" s="3">
+        <v>95.58</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>22</v>
+      </c>
+      <c r="B180" t="s">
+        <v>34</v>
+      </c>
+      <c r="C180" t="s">
+        <v>38</v>
+      </c>
+      <c r="D180" t="s">
+        <v>232</v>
+      </c>
+      <c r="E180" t="s">
+        <v>254</v>
+      </c>
+      <c r="F180" s="3">
+        <v>1618.59</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>22</v>
+      </c>
+      <c r="B181" t="s">
+        <v>34</v>
+      </c>
+      <c r="C181" t="s">
+        <v>38</v>
+      </c>
+      <c r="D181" t="s">
+        <v>233</v>
+      </c>
+      <c r="E181" t="s">
+        <v>254</v>
+      </c>
+      <c r="F181" s="3">
+        <v>178.45</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>22</v>
+      </c>
+      <c r="B182" t="s">
+        <v>34</v>
+      </c>
+      <c r="C182" t="s">
+        <v>38</v>
+      </c>
+      <c r="D182" t="s">
+        <v>234</v>
+      </c>
+      <c r="E182" t="s">
+        <v>254</v>
+      </c>
+      <c r="F182" s="3">
+        <v>247.24</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>22</v>
+      </c>
+      <c r="B183" t="s">
+        <v>34</v>
+      </c>
+      <c r="C183" t="s">
+        <v>38</v>
+      </c>
+      <c r="D183" t="s">
+        <v>235</v>
+      </c>
+      <c r="E183" t="s">
+        <v>254</v>
+      </c>
+      <c r="F183" s="3">
+        <v>145.46</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F151"/>
+  <autoFilter ref="A1:F183"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -4997,28 +5814,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5026,7 +5843,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>12</v>
@@ -5052,10 +5869,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -5078,10 +5895,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -5104,10 +5921,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5130,10 +5947,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -5156,7 +5973,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -5182,7 +5999,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>14</v>
@@ -5208,7 +6025,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>14</v>
@@ -5234,7 +6051,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>14</v>
@@ -5260,7 +6077,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>14</v>
@@ -5286,7 +6103,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>14</v>
@@ -5309,13 +6126,13 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>236</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>237</v>
+        <v>34</v>
       </c>
       <c r="C13">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -5330,6 +6147,32 @@
         <v>1</v>
       </c>
       <c r="H13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14">
+        <v>182</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5340,7 +6183,126 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>278</v>
+      </c>
+      <c r="B8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -5351,22 +6313,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>246</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5374,19 +6336,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5394,19 +6356,19 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
       <c r="E3" s="9" t="s">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5414,19 +6376,19 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" s="9" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5434,19 +6396,19 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" s="9" t="s">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5454,19 +6416,19 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
         <v>36</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>251</v>
+        <v>294</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>262</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5474,19 +6436,19 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>263</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5494,19 +6456,19 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5514,19 +6476,19 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -5534,19 +6496,19 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5554,19 +6516,19 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5574,19 +6536,39 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>268</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
